--- a/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yohai\Downloads\html5up-dimension\assets\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE0ECA0-AC99-40C9-B3B4-C3D695FF9D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5ED694-2308-462D-81F8-EF4C2ABFC380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -52,98 +52,107 @@
     <t>Option :</t>
   </si>
   <si>
+    <t>▸Collecter, suivre et orienter des demandes 
+▸Traiter des demandes concernant les services réseau et système, applicatifs
+▸Traiter des demandes concernant les applications</t>
+  </si>
+  <si>
+    <t>▸Participer à la valorisation de l’image de l’organisation sur les médias numériques en tenant compte du cadre juridique et des enjeux économiques
+▸Référencer les services en ligne de l’organisation et mesurer leur visibilité.
+▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
+  </si>
+  <si>
+    <t>▸Analyser les objectifs et les modalités d’organisation d’un projet
+▸Planifier les activités
+▸Évaluer les indicateurs de suivi d’un projet et analyser les écarts</t>
+  </si>
+  <si>
+    <t>▸Réaliser les tests d’intégration et d’acceptation d’un service
+▸Déployer un service
+▸Accompagner les utilisateurs dans la mise en place d’un service</t>
+  </si>
+  <si>
+    <t>▸Mettre en place son environnement d’apprentissage personnel
+▸Mettre en œuvre des outils et stratégies de veille informationnelle
+▸Gérer son identité professionnelle
+▸Développer son projet professionnel</t>
+  </si>
+  <si>
+    <t>▢ SISR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réalisation en cours de formation
+</t>
+  </si>
+  <si>
+    <t>Compétences mises en œuvre
+Réalisations professionnelles
+(intitulé et liste des documents et productions associés)</t>
+  </si>
+  <si>
+    <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de première année</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de seconde année</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>NOM et prénom :  HAGEGE YOHAI</t>
+  </si>
+  <si>
+    <t>Centre de formation : ORT DANIEL MEYER</t>
+  </si>
+  <si>
+    <t>X SLAM</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://yohaihagege.github.io/PORTEFOLIO/#</t>
+  </si>
+  <si>
+    <t>N° candidat : 2542597011</t>
+  </si>
+  <si>
+    <t>CoffreMotDePasse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Hazara Bésimha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porte folio </t>
+  </si>
+  <si>
+    <t>GESTTRAVAUX java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izicerfa lite </t>
+  </si>
+  <si>
+    <t>seat planning</t>
+  </si>
+  <si>
     <t>▸Recenser et identifier les ressources numériques 
-▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatique
+▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatiquxe
 ▸Mettre en place et vérifier les niveaux d’habilitation associés à un service
 ▸Vérifier les conditions de la continuité d’un service informatique
 ▸Gérer des sauvegardes
 ▸Vérifier le respect des règles d’utilisation des ressources numériques</t>
   </si>
   <si>
-    <t>▸Collecter, suivre et orienter des demandes 
-▸Traiter des demandes concernant les services réseau et système, applicatifs
-▸Traiter des demandes concernant les applications</t>
-  </si>
-  <si>
-    <t>▸Participer à la valorisation de l’image de l’organisation sur les médias numériques en tenant compte du cadre juridique et des enjeux économiques
-▸Référencer les services en ligne de l’organisation et mesurer leur visibilité.
-▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
-  </si>
-  <si>
-    <t>▸Analyser les objectifs et les modalités d’organisation d’un projet
-▸Planifier les activités
-▸Évaluer les indicateurs de suivi d’un projet et analyser les écarts</t>
-  </si>
-  <si>
-    <t>▸Réaliser les tests d’intégration et d’acceptation d’un service
-▸Déployer un service
-▸Accompagner les utilisateurs dans la mise en place d’un service</t>
-  </si>
-  <si>
-    <t>▸Mettre en place son environnement d’apprentissage personnel
-▸Mettre en œuvre des outils et stratégies de veille informationnelle
-▸Gérer son identité professionnelle
-▸Développer son projet professionnel</t>
-  </si>
-  <si>
-    <t>▢ SISR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réalisation en cours de formation
-</t>
-  </si>
-  <si>
-    <t>Compétences mises en œuvre
-Réalisations professionnelles
-(intitulé et liste des documents et productions associés)</t>
-  </si>
-  <si>
-    <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
-  </si>
-  <si>
-    <t>Réalisations en milieu professionnel en cours de première année</t>
-  </si>
-  <si>
-    <t>Réalisations en milieu professionnel en cours de seconde année</t>
-  </si>
-  <si>
-    <t>SESSION 2026</t>
-  </si>
-  <si>
-    <t>NOM et prénom :  HAGEGE YOHAI</t>
-  </si>
-  <si>
-    <t>Centre de formation : ORT DANIEL MEYER</t>
-  </si>
-  <si>
-    <t>X SLAM</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio : https://yohaihagege.github.io/PORTEFOLIO/#</t>
-  </si>
-  <si>
-    <t>N° candidat : 2542597011</t>
-  </si>
-  <si>
-    <t>CoffreMotDePasse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Hazara Bésimha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">porte folio </t>
-  </si>
-  <si>
-    <t>GESTTRAVAUX java</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izicerfa lite </t>
+    <t>GESTTRAVAUX web</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -615,7 +624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -638,12 +647,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -683,6 +686,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -749,8 +755,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1071,84 +1077,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="44"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="37"/>
+      <c r="H3" s="43"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="21" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1170,25 +1176,25 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="F7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="44" t="s">
         <v>13</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1227,16 +1233,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="A8" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1274,22 +1280,24 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="16"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1327,18 +1335,24 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="16" t="s">
+      <c r="A10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16" t="s">
+        <v>36</v>
+      </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1376,17 +1390,21 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="45" t="s">
-        <v>29</v>
+      <c r="A11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1425,14 +1443,18 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16" t="s">
+        <v>36</v>
+      </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1470,14 +1492,18 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1515,14 +1541,14 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1560,14 +1586,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1605,14 +1631,14 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1650,14 +1676,14 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1695,14 +1721,14 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1740,16 +1766,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="31"/>
+      <c r="A19" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1787,22 +1813,22 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="C20" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1840,14 +1866,14 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1885,14 +1911,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1930,14 +1956,14 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1975,14 +2001,14 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2020,14 +2046,14 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2065,14 +2091,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2110,16 +2136,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="A27" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2157,16 +2183,20 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
+      <c r="A28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2204,14 +2234,14 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2249,14 +2279,14 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2294,14 +2324,14 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2339,14 +2369,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2384,14 +2414,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2429,14 +2459,14 @@
       <c r="AQ33"/>
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>

--- a/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yohai\Downloads\html5up-dimension\assets\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5ED694-2308-462D-81F8-EF4C2ABFC380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA90E57-75F4-465E-882B-A4B9128EEA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>GESTTRAVAUX web</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -689,15 +686,42 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -730,33 +754,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1077,56 +1074,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="42" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="43"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="31"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1138,22 +1135,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1176,8 +1173,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="20" t="s">
         <v>34</v>
       </c>
@@ -1193,7 +1190,7 @@
       <c r="G7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="22" t="s">
         <v>13</v>
       </c>
       <c r="I7"/>
@@ -1233,16 +1230,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1294,7 +1291,7 @@
       <c r="F9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>28</v>
       </c>
       <c r="H9" s="16"/>
@@ -1343,15 +1340,15 @@
         <v>28</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="15"/>
-      <c r="H10" s="16" t="s">
-        <v>36</v>
+      <c r="H10" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1397,10 +1394,10 @@
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="21" t="s">
@@ -1452,8 +1449,8 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
-      <c r="H12" s="16" t="s">
-        <v>36</v>
+      <c r="H12" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1499,7 +1496,7 @@
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="15"/>
@@ -1766,16 +1763,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2136,16 +2133,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2187,12 +2184,12 @@
         <v>32</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="15"/>
@@ -2596,11 +2593,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2608,6 +2600,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
+++ b/assets/doc/8_-_ANNEXE_VI.1_-_EPREUVE_E5_TABLEAU_DE_SYNTHESE_-_BTS_SIO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yohai\Downloads\html5up-dimension\assets\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA90E57-75F4-465E-882B-A4B9128EEA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4C193B-2B70-4019-BAF7-CD22917F6CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>Hazara Bésimha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">porte folio </t>
   </si>
   <si>
     <t>GESTTRAVAUX java</t>
@@ -150,6 +147,9 @@
   </si>
   <si>
     <t>GESTTRAVAUX web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portfolio </t>
   </si>
 </sst>
 </file>
@@ -689,9 +689,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -714,45 +753,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1074,56 +1074,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="23"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="30" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="31"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1135,22 +1135,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="32" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1173,10 +1173,10 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>9</v>
@@ -1230,16 +1230,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="14" t="s">
@@ -1388,11 +1388,15 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B11" s="8"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="C11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
         <v>28</v>
@@ -1441,10 +1445,12 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
@@ -1490,10 +1496,12 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
@@ -1763,16 +1771,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2133,16 +2141,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2181,7 +2189,7 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="14" t="s">
@@ -2192,7 +2200,9 @@
       <c r="F28" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="15"/>
+      <c r="G28" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H28" s="16"/>
       <c r="I28"/>
       <c r="J28"/>
@@ -2593,6 +2603,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2600,11 +2615,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
